--- a/vignettes/vignette-1/target_profile_table.xlsx
+++ b/vignettes/vignette-1/target_profile_table.xlsx
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="H2" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>0.25</v>

--- a/vignettes/vignette-1/target_profile_table.xlsx
+++ b/vignettes/vignette-1/target_profile_table.xlsx
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="H2" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="I2" t="n">
         <v>8</v>
